--- a/Carbon/d13C_Sediment.xlsx
+++ b/Carbon/d13C_Sediment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11023"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lukaseamus/Desktop/PhD/Papers/Burial/kelp-burial/Carbon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4962F0F1-38CD-9D41-B510-01959D0BCA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4157833B-13BA-0645-A0D5-3B07AB272629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="660" windowWidth="18980" windowHeight="18720" xr2:uid="{D120C0EF-290F-244A-AE4B-CB2F7CD281C3}"/>
+    <workbookView xWindow="19260" yWindow="660" windowWidth="18980" windowHeight="18720" xr2:uid="{D120C0EF-290F-244A-AE4B-CB2F7CD281C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="704">
   <si>
     <t>ID</t>
   </si>
@@ -1632,6 +1632,522 @@
   </si>
   <si>
     <t>L_2_1_2</t>
+  </si>
+  <si>
+    <t>26.10.26</t>
+  </si>
+  <si>
+    <t>E_1_1_1</t>
+  </si>
+  <si>
+    <t>E_1_1_10</t>
+  </si>
+  <si>
+    <t>E_1_1_2</t>
+  </si>
+  <si>
+    <t>E_1_1_3</t>
+  </si>
+  <si>
+    <t>E_1_1_4</t>
+  </si>
+  <si>
+    <t>E_1_1_5</t>
+  </si>
+  <si>
+    <t>E_1_1_6</t>
+  </si>
+  <si>
+    <t>E_1_1_7</t>
+  </si>
+  <si>
+    <t>E_1_1_8</t>
+  </si>
+  <si>
+    <t>E_1_1_9</t>
+  </si>
+  <si>
+    <t>E_1_3_1</t>
+  </si>
+  <si>
+    <t>E_1_3_10</t>
+  </si>
+  <si>
+    <t>E_1_3_2</t>
+  </si>
+  <si>
+    <t>E_1_3_3</t>
+  </si>
+  <si>
+    <t>E_1_3_4</t>
+  </si>
+  <si>
+    <t>E_1_3_5</t>
+  </si>
+  <si>
+    <t>E_1_3_6</t>
+  </si>
+  <si>
+    <t>E_1_3_7</t>
+  </si>
+  <si>
+    <t>E_1_3_8</t>
+  </si>
+  <si>
+    <t>E_1_3_9</t>
+  </si>
+  <si>
+    <t>E_1_4_1</t>
+  </si>
+  <si>
+    <t>E_1_4_10</t>
+  </si>
+  <si>
+    <t>E_1_4_2</t>
+  </si>
+  <si>
+    <t>E_1_4_3</t>
+  </si>
+  <si>
+    <t>E_1_4_4</t>
+  </si>
+  <si>
+    <t>E_1_4_5</t>
+  </si>
+  <si>
+    <t>E_1_4_6</t>
+  </si>
+  <si>
+    <t>E_1_4_7</t>
+  </si>
+  <si>
+    <t>E_1_4_8</t>
+  </si>
+  <si>
+    <t>E_1_4_9</t>
+  </si>
+  <si>
+    <t>E_1_5_1</t>
+  </si>
+  <si>
+    <t>E_1_5_10</t>
+  </si>
+  <si>
+    <t>E_1_5_2</t>
+  </si>
+  <si>
+    <t>E_1_5_3</t>
+  </si>
+  <si>
+    <t>E_1_5_4</t>
+  </si>
+  <si>
+    <t>E_1_5_5</t>
+  </si>
+  <si>
+    <t>E_1_5_6</t>
+  </si>
+  <si>
+    <t>E_1_5_7</t>
+  </si>
+  <si>
+    <t>E_1_5_8</t>
+  </si>
+  <si>
+    <t>E_1_5_9</t>
+  </si>
+  <si>
+    <t>E_1_7_1</t>
+  </si>
+  <si>
+    <t>E_1_7_10</t>
+  </si>
+  <si>
+    <t>E_1_7_2</t>
+  </si>
+  <si>
+    <t>E_1_7_3</t>
+  </si>
+  <si>
+    <t>E_1_7_4</t>
+  </si>
+  <si>
+    <t>E_1_7_5</t>
+  </si>
+  <si>
+    <t>E_1_7_6</t>
+  </si>
+  <si>
+    <t>E_1_7_7</t>
+  </si>
+  <si>
+    <t>E_1_7_8</t>
+  </si>
+  <si>
+    <t>E_1_7_9</t>
+  </si>
+  <si>
+    <t>E_1_9_3</t>
+  </si>
+  <si>
+    <t>E_2_1_1</t>
+  </si>
+  <si>
+    <t>E_2_1_10</t>
+  </si>
+  <si>
+    <t>E_2_1_2</t>
+  </si>
+  <si>
+    <t>E_2_1_3</t>
+  </si>
+  <si>
+    <t>E_2_1_4</t>
+  </si>
+  <si>
+    <t>E_2_1_5</t>
+  </si>
+  <si>
+    <t>E_2_1_6</t>
+  </si>
+  <si>
+    <t>E_2_1_7</t>
+  </si>
+  <si>
+    <t>E_2_1_8</t>
+  </si>
+  <si>
+    <t>E_2_1_9</t>
+  </si>
+  <si>
+    <t>E_2_11_1</t>
+  </si>
+  <si>
+    <t>E_2_11_10</t>
+  </si>
+  <si>
+    <t>E_2_11_2</t>
+  </si>
+  <si>
+    <t>E_2_11_3</t>
+  </si>
+  <si>
+    <t>E_2_11_4</t>
+  </si>
+  <si>
+    <t>E_2_11_5</t>
+  </si>
+  <si>
+    <t>E_2_11_6</t>
+  </si>
+  <si>
+    <t>E_2_11_7</t>
+  </si>
+  <si>
+    <t>E_2_11_8</t>
+  </si>
+  <si>
+    <t>E_2_11_9</t>
+  </si>
+  <si>
+    <t>E_2_14_1</t>
+  </si>
+  <si>
+    <t>E_2_14_10</t>
+  </si>
+  <si>
+    <t>E_2_14_2</t>
+  </si>
+  <si>
+    <t>E_2_14_3</t>
+  </si>
+  <si>
+    <t>E_2_14_4</t>
+  </si>
+  <si>
+    <t>E_2_14_5</t>
+  </si>
+  <si>
+    <t>E_2_14_6</t>
+  </si>
+  <si>
+    <t>E_2_14_7</t>
+  </si>
+  <si>
+    <t>E_2_14_8</t>
+  </si>
+  <si>
+    <t>E_2_14_9</t>
+  </si>
+  <si>
+    <t>E_2_15_1</t>
+  </si>
+  <si>
+    <t>E_2_15_10</t>
+  </si>
+  <si>
+    <t>E_2_15_2</t>
+  </si>
+  <si>
+    <t>E_2_15_3</t>
+  </si>
+  <si>
+    <t>E_2_15_4</t>
+  </si>
+  <si>
+    <t>E_2_15_5</t>
+  </si>
+  <si>
+    <t>E_2_15_6</t>
+  </si>
+  <si>
+    <t>E_2_15_7</t>
+  </si>
+  <si>
+    <t>E_2_15_8</t>
+  </si>
+  <si>
+    <t>E_2_15_9</t>
+  </si>
+  <si>
+    <t>E_2_2_1</t>
+  </si>
+  <si>
+    <t>E_2_2_10</t>
+  </si>
+  <si>
+    <t>E_2_2_2</t>
+  </si>
+  <si>
+    <t>E_2_2_3</t>
+  </si>
+  <si>
+    <t>E_2_2_4</t>
+  </si>
+  <si>
+    <t>E_2_2_5</t>
+  </si>
+  <si>
+    <t>E_2_2_6</t>
+  </si>
+  <si>
+    <t>E_2_2_7</t>
+  </si>
+  <si>
+    <t>E_2_2_8</t>
+  </si>
+  <si>
+    <t>E_2_2_9</t>
+  </si>
+  <si>
+    <t>E_2_3_1</t>
+  </si>
+  <si>
+    <t>E_2_3_10</t>
+  </si>
+  <si>
+    <t>E_2_3_2</t>
+  </si>
+  <si>
+    <t>E_2_3_3</t>
+  </si>
+  <si>
+    <t>E_2_3_4</t>
+  </si>
+  <si>
+    <t>E_2_3_5</t>
+  </si>
+  <si>
+    <t>E_2_3_6</t>
+  </si>
+  <si>
+    <t>E_2_3_7</t>
+  </si>
+  <si>
+    <t>E_2_3_8</t>
+  </si>
+  <si>
+    <t>E_2_3_9</t>
+  </si>
+  <si>
+    <t>E_2_4_1</t>
+  </si>
+  <si>
+    <t>E_2_4_10</t>
+  </si>
+  <si>
+    <t>E_2_4_2</t>
+  </si>
+  <si>
+    <t>E_2_4_3</t>
+  </si>
+  <si>
+    <t>E_2_4_4</t>
+  </si>
+  <si>
+    <t>E_2_4_5</t>
+  </si>
+  <si>
+    <t>E_2_4_6</t>
+  </si>
+  <si>
+    <t>E_2_4_7</t>
+  </si>
+  <si>
+    <t>E_2_4_8</t>
+  </si>
+  <si>
+    <t>E_2_4_9</t>
+  </si>
+  <si>
+    <t>E_2_5_1</t>
+  </si>
+  <si>
+    <t>E_2_5_10</t>
+  </si>
+  <si>
+    <t>E_2_5_2</t>
+  </si>
+  <si>
+    <t>E_2_5_3</t>
+  </si>
+  <si>
+    <t>E_2_5_4</t>
+  </si>
+  <si>
+    <t>E_2_5_5</t>
+  </si>
+  <si>
+    <t>E_2_5_6</t>
+  </si>
+  <si>
+    <t>E_2_5_7</t>
+  </si>
+  <si>
+    <t>E_2_5_8</t>
+  </si>
+  <si>
+    <t>E_2_5_9</t>
+  </si>
+  <si>
+    <t>E_2_6_1</t>
+  </si>
+  <si>
+    <t>E_2_6_10</t>
+  </si>
+  <si>
+    <t>E_2_6_2</t>
+  </si>
+  <si>
+    <t>E_2_6_3</t>
+  </si>
+  <si>
+    <t>E_2_6_4</t>
+  </si>
+  <si>
+    <t>E_2_6_5</t>
+  </si>
+  <si>
+    <t>E_2_6_6</t>
+  </si>
+  <si>
+    <t>E_2_6_7</t>
+  </si>
+  <si>
+    <t>E_2_6_8</t>
+  </si>
+  <si>
+    <t>E_2_6_9</t>
+  </si>
+  <si>
+    <t>E_2_8_1</t>
+  </si>
+  <si>
+    <t>E_2_8_10</t>
+  </si>
+  <si>
+    <t>E_2_8_2</t>
+  </si>
+  <si>
+    <t>E_2_8_3</t>
+  </si>
+  <si>
+    <t>E_2_8_4</t>
+  </si>
+  <si>
+    <t>E_2_8_5</t>
+  </si>
+  <si>
+    <t>E_2_8_6</t>
+  </si>
+  <si>
+    <t>E_2_8_7</t>
+  </si>
+  <si>
+    <t>E_2_8_8</t>
+  </si>
+  <si>
+    <t>E_2_8_9</t>
+  </si>
+  <si>
+    <t>E_2_9_1</t>
+  </si>
+  <si>
+    <t>E_2_9_10</t>
+  </si>
+  <si>
+    <t>E_2_9_2</t>
+  </si>
+  <si>
+    <t>E_2_9_3</t>
+  </si>
+  <si>
+    <t>E_2_9_4</t>
+  </si>
+  <si>
+    <t>E_2_9_5</t>
+  </si>
+  <si>
+    <t>E_2_9_6</t>
+  </si>
+  <si>
+    <t>E_2_9_7</t>
+  </si>
+  <si>
+    <t>E_2_9_8</t>
+  </si>
+  <si>
+    <t>E_2_9_9</t>
+  </si>
+  <si>
+    <t>E_C_1_2_1</t>
+  </si>
+  <si>
+    <t>E_C_1_2_2</t>
+  </si>
+  <si>
+    <t>E_C_1_2_5</t>
+  </si>
+  <si>
+    <t>E_C_2_1_10</t>
+  </si>
+  <si>
+    <t>E_C_2_1_2</t>
+  </si>
+  <si>
+    <t>E_C_2_2_5</t>
+  </si>
+  <si>
+    <t>E_C_2_2_8</t>
+  </si>
+  <si>
+    <t>E_C_2_2_9</t>
+  </si>
+  <si>
+    <t>L_2_3_2</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -2017,7 +2533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18AC6222-1A29-714F-879C-A900060CD8DA}">
-  <dimension ref="A1:N562"/>
+  <dimension ref="A1:N735"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
@@ -14956,6 +15472,3985 @@
         <v>0</v>
       </c>
     </row>
+    <row r="563" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A563" t="s">
+        <v>532</v>
+      </c>
+      <c r="B563" t="s">
+        <v>533</v>
+      </c>
+      <c r="C563" t="s">
+        <v>703</v>
+      </c>
+      <c r="D563">
+        <v>13.279012240425736</v>
+      </c>
+      <c r="E563">
+        <v>212.58567553963039</v>
+      </c>
+      <c r="F563" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G563" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A564" t="s">
+        <v>532</v>
+      </c>
+      <c r="B564" t="s">
+        <v>534</v>
+      </c>
+      <c r="C564" t="s">
+        <v>703</v>
+      </c>
+      <c r="D564">
+        <v>3.3523844474945328</v>
+      </c>
+      <c r="E564">
+        <v>-14.911697243303294</v>
+      </c>
+      <c r="F564" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G564" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A565" t="s">
+        <v>532</v>
+      </c>
+      <c r="B565" t="s">
+        <v>535</v>
+      </c>
+      <c r="C565" t="s">
+        <v>703</v>
+      </c>
+      <c r="D565">
+        <v>4.6860562398200498</v>
+      </c>
+      <c r="E565">
+        <v>-0.89465920489730522</v>
+      </c>
+      <c r="F565" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G565" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A566" t="s">
+        <v>532</v>
+      </c>
+      <c r="B566" t="s">
+        <v>536</v>
+      </c>
+      <c r="C566" t="s">
+        <v>703</v>
+      </c>
+      <c r="D566">
+        <v>5.5060206046109412</v>
+      </c>
+      <c r="E566">
+        <v>-5.3316174111963228</v>
+      </c>
+      <c r="F566" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G566" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A567" t="s">
+        <v>532</v>
+      </c>
+      <c r="B567" t="s">
+        <v>537</v>
+      </c>
+      <c r="C567" t="s">
+        <v>703</v>
+      </c>
+      <c r="D567">
+        <v>6.0260513160261642</v>
+      </c>
+      <c r="E567">
+        <v>-9.4430997375000274</v>
+      </c>
+      <c r="F567" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G567" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="568" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A568" t="s">
+        <v>532</v>
+      </c>
+      <c r="B568" t="s">
+        <v>538</v>
+      </c>
+      <c r="C568" t="s">
+        <v>703</v>
+      </c>
+      <c r="D568">
+        <v>7.4361557018618338</v>
+      </c>
+      <c r="E568">
+        <v>-11.245688589754529</v>
+      </c>
+      <c r="F568" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G568" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="569" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A569" t="s">
+        <v>532</v>
+      </c>
+      <c r="B569" t="s">
+        <v>539</v>
+      </c>
+      <c r="C569" t="s">
+        <v>703</v>
+      </c>
+      <c r="D569">
+        <v>6.9686168603609362</v>
+      </c>
+      <c r="E569">
+        <v>-12.638689338914796</v>
+      </c>
+      <c r="F569" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G569" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A570" t="s">
+        <v>532</v>
+      </c>
+      <c r="B570" t="s">
+        <v>540</v>
+      </c>
+      <c r="C570" t="s">
+        <v>703</v>
+      </c>
+      <c r="D570">
+        <v>5.3628809157661914</v>
+      </c>
+      <c r="E570">
+        <v>-14.002280806994916</v>
+      </c>
+      <c r="F570" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G570" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A571" t="s">
+        <v>532</v>
+      </c>
+      <c r="B571" t="s">
+        <v>541</v>
+      </c>
+      <c r="C571" t="s">
+        <v>703</v>
+      </c>
+      <c r="D571">
+        <v>5.3837599880810236</v>
+      </c>
+      <c r="E571">
+        <v>-13.684436380438692</v>
+      </c>
+      <c r="F571" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G571" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A572" t="s">
+        <v>532</v>
+      </c>
+      <c r="B572" t="s">
+        <v>542</v>
+      </c>
+      <c r="C572" t="s">
+        <v>703</v>
+      </c>
+      <c r="D572">
+        <v>5.5330382283576309</v>
+      </c>
+      <c r="E572">
+        <v>-14.199401456887557</v>
+      </c>
+      <c r="F572" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G572" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A573" t="s">
+        <v>532</v>
+      </c>
+      <c r="B573" t="s">
+        <v>503</v>
+      </c>
+      <c r="C573" t="s">
+        <v>703</v>
+      </c>
+      <c r="D573">
+        <v>4.1938876753635048</v>
+      </c>
+      <c r="E573">
+        <v>-11.193704715775496</v>
+      </c>
+      <c r="F573" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G573" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A574" t="s">
+        <v>532</v>
+      </c>
+      <c r="B574" t="s">
+        <v>504</v>
+      </c>
+      <c r="C574" t="s">
+        <v>703</v>
+      </c>
+      <c r="D574">
+        <v>3.848044103563999</v>
+      </c>
+      <c r="E574">
+        <v>-6.9450180953653877</v>
+      </c>
+      <c r="F574" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G574" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A575" t="s">
+        <v>532</v>
+      </c>
+      <c r="B575" t="s">
+        <v>543</v>
+      </c>
+      <c r="C575" t="s">
+        <v>703</v>
+      </c>
+      <c r="D575">
+        <v>9.5751296620433184</v>
+      </c>
+      <c r="E575">
+        <v>188.49544140497747</v>
+      </c>
+      <c r="F575" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G575" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A576" t="s">
+        <v>532</v>
+      </c>
+      <c r="B576" t="s">
+        <v>544</v>
+      </c>
+      <c r="C576" t="s">
+        <v>703</v>
+      </c>
+      <c r="D576">
+        <v>3.757577025316341</v>
+      </c>
+      <c r="E576">
+        <v>-15.871730667856845</v>
+      </c>
+      <c r="F576" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G576" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A577" t="s">
+        <v>532</v>
+      </c>
+      <c r="B577" t="s">
+        <v>545</v>
+      </c>
+      <c r="C577" t="s">
+        <v>703</v>
+      </c>
+      <c r="D577">
+        <v>5.9629216996284766</v>
+      </c>
+      <c r="E577">
+        <v>7.445383732722501</v>
+      </c>
+      <c r="F577" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G577" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A578" t="s">
+        <v>532</v>
+      </c>
+      <c r="B578" t="s">
+        <v>546</v>
+      </c>
+      <c r="C578" t="s">
+        <v>703</v>
+      </c>
+      <c r="D578">
+        <v>7.0615709388994068</v>
+      </c>
+      <c r="E578">
+        <v>-0.39373134090461193</v>
+      </c>
+      <c r="F578" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G578" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A579" t="s">
+        <v>532</v>
+      </c>
+      <c r="B579" t="s">
+        <v>547</v>
+      </c>
+      <c r="C579" t="s">
+        <v>703</v>
+      </c>
+      <c r="D579">
+        <v>6.9309401815326748</v>
+      </c>
+      <c r="E579">
+        <v>-5.2349973381211861</v>
+      </c>
+      <c r="F579" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G579" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A580" t="s">
+        <v>532</v>
+      </c>
+      <c r="B580" t="s">
+        <v>548</v>
+      </c>
+      <c r="C580" t="s">
+        <v>703</v>
+      </c>
+      <c r="D580">
+        <v>9.1653241339012279</v>
+      </c>
+      <c r="E580">
+        <v>-9.4380655498143255</v>
+      </c>
+      <c r="F580" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G580" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A581" t="s">
+        <v>532</v>
+      </c>
+      <c r="B581" t="s">
+        <v>549</v>
+      </c>
+      <c r="C581" t="s">
+        <v>703</v>
+      </c>
+      <c r="D581">
+        <v>7.9388046017719098</v>
+      </c>
+      <c r="E581">
+        <v>-10.641163857996808</v>
+      </c>
+      <c r="F581" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G581" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A582" t="s">
+        <v>532</v>
+      </c>
+      <c r="B582" t="s">
+        <v>550</v>
+      </c>
+      <c r="C582" t="s">
+        <v>703</v>
+      </c>
+      <c r="D582">
+        <v>6.8659722739448874</v>
+      </c>
+      <c r="E582">
+        <v>-12.448360856952368</v>
+      </c>
+      <c r="F582" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G582" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A583" t="s">
+        <v>532</v>
+      </c>
+      <c r="B583" t="s">
+        <v>551</v>
+      </c>
+      <c r="C583" t="s">
+        <v>703</v>
+      </c>
+      <c r="D583">
+        <v>8.0783498701207339</v>
+      </c>
+      <c r="E583">
+        <v>-13.276314054287743</v>
+      </c>
+      <c r="F583" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G583" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A584" t="s">
+        <v>532</v>
+      </c>
+      <c r="B584" t="s">
+        <v>552</v>
+      </c>
+      <c r="C584" t="s">
+        <v>703</v>
+      </c>
+      <c r="D584">
+        <v>6.9325890971807889</v>
+      </c>
+      <c r="E584">
+        <v>-13.974283953187868</v>
+      </c>
+      <c r="F584" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G584" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="585" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A585" t="s">
+        <v>532</v>
+      </c>
+      <c r="B585" t="s">
+        <v>553</v>
+      </c>
+      <c r="C585" t="s">
+        <v>703</v>
+      </c>
+      <c r="D585">
+        <v>1.3892314050873025</v>
+      </c>
+      <c r="E585">
+        <v>355.47064593782761</v>
+      </c>
+      <c r="F585" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G585" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A586" t="s">
+        <v>532</v>
+      </c>
+      <c r="B586" t="s">
+        <v>554</v>
+      </c>
+      <c r="C586" t="s">
+        <v>703</v>
+      </c>
+      <c r="D586">
+        <v>0.12494808565194995</v>
+      </c>
+      <c r="E586">
+        <v>5.7599520125791308</v>
+      </c>
+      <c r="F586" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G586" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A587" t="s">
+        <v>532</v>
+      </c>
+      <c r="B587" t="s">
+        <v>555</v>
+      </c>
+      <c r="C587" t="s">
+        <v>703</v>
+      </c>
+      <c r="D587">
+        <v>0.21971480930478515</v>
+      </c>
+      <c r="E587">
+        <v>120.53003051965348</v>
+      </c>
+      <c r="F587" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G587" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A588" t="s">
+        <v>532</v>
+      </c>
+      <c r="B588" t="s">
+        <v>556</v>
+      </c>
+      <c r="C588" t="s">
+        <v>703</v>
+      </c>
+      <c r="D588">
+        <v>0.15660369644954567</v>
+      </c>
+      <c r="E588">
+        <v>2.2146120221527994</v>
+      </c>
+      <c r="F588" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G588" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A589" t="s">
+        <v>532</v>
+      </c>
+      <c r="B589" t="s">
+        <v>557</v>
+      </c>
+      <c r="C589" t="s">
+        <v>703</v>
+      </c>
+      <c r="D589">
+        <v>0.17239418851359248</v>
+      </c>
+      <c r="E589">
+        <v>-8.0404150668364487</v>
+      </c>
+      <c r="F589" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G589" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A590" t="s">
+        <v>532</v>
+      </c>
+      <c r="B590" t="s">
+        <v>558</v>
+      </c>
+      <c r="C590" t="s">
+        <v>703</v>
+      </c>
+      <c r="D590">
+        <v>0.18292357560834549</v>
+      </c>
+      <c r="E590">
+        <v>-2.5607031696999272</v>
+      </c>
+      <c r="F590" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G590" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A591" t="s">
+        <v>532</v>
+      </c>
+      <c r="B591" t="s">
+        <v>559</v>
+      </c>
+      <c r="C591" t="s">
+        <v>703</v>
+      </c>
+      <c r="D591">
+        <v>0.13380662691087289</v>
+      </c>
+      <c r="E591">
+        <v>1.7210078145852279</v>
+      </c>
+      <c r="F591" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G591" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A592" t="s">
+        <v>532</v>
+      </c>
+      <c r="B592" t="s">
+        <v>560</v>
+      </c>
+      <c r="C592" t="s">
+        <v>703</v>
+      </c>
+      <c r="D592">
+        <v>0.1285911731350956</v>
+      </c>
+      <c r="E592">
+        <v>0.45017134147771998</v>
+      </c>
+      <c r="F592" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G592" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A593" t="s">
+        <v>532</v>
+      </c>
+      <c r="B593" t="s">
+        <v>561</v>
+      </c>
+      <c r="C593" t="s">
+        <v>703</v>
+      </c>
+      <c r="D593">
+        <v>0.1094931299600363</v>
+      </c>
+      <c r="E593">
+        <v>5.2660127167943216E-2</v>
+      </c>
+      <c r="F593" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G593" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A594" t="s">
+        <v>532</v>
+      </c>
+      <c r="B594" t="s">
+        <v>562</v>
+      </c>
+      <c r="C594" t="s">
+        <v>703</v>
+      </c>
+      <c r="D594">
+        <v>0.12320797253892538</v>
+      </c>
+      <c r="E594">
+        <v>4.2941176143307622</v>
+      </c>
+      <c r="F594" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G594" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A595" t="s">
+        <v>532</v>
+      </c>
+      <c r="B595" t="s">
+        <v>563</v>
+      </c>
+      <c r="C595" t="s">
+        <v>703</v>
+      </c>
+      <c r="D595">
+        <v>14.224098068708816</v>
+      </c>
+      <c r="E595">
+        <v>207.42935960939801</v>
+      </c>
+      <c r="F595" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G595" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A596" t="s">
+        <v>532</v>
+      </c>
+      <c r="B596" t="s">
+        <v>564</v>
+      </c>
+      <c r="C596" t="s">
+        <v>703</v>
+      </c>
+      <c r="D596">
+        <v>3.0836356931804954</v>
+      </c>
+      <c r="E596">
+        <v>-16.694945988243305</v>
+      </c>
+      <c r="F596" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G596" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A597" t="s">
+        <v>532</v>
+      </c>
+      <c r="B597" t="s">
+        <v>565</v>
+      </c>
+      <c r="C597" t="s">
+        <v>703</v>
+      </c>
+      <c r="D597">
+        <v>6.2928107244866736</v>
+      </c>
+      <c r="E597">
+        <v>2.904848312096469</v>
+      </c>
+      <c r="F597" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G597" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A598" t="s">
+        <v>532</v>
+      </c>
+      <c r="B598" t="s">
+        <v>566</v>
+      </c>
+      <c r="C598" t="s">
+        <v>703</v>
+      </c>
+      <c r="D598">
+        <v>4.0177728276626272</v>
+      </c>
+      <c r="E598">
+        <v>-0.7662038562723481</v>
+      </c>
+      <c r="F598" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G598" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A599" t="s">
+        <v>532</v>
+      </c>
+      <c r="B599" t="s">
+        <v>567</v>
+      </c>
+      <c r="C599" t="s">
+        <v>703</v>
+      </c>
+      <c r="D599">
+        <v>3.7408592523136019</v>
+      </c>
+      <c r="E599">
+        <v>-6.3192610142904648</v>
+      </c>
+      <c r="F599" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G599" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A600" t="s">
+        <v>532</v>
+      </c>
+      <c r="B600" t="s">
+        <v>568</v>
+      </c>
+      <c r="C600" t="s">
+        <v>703</v>
+      </c>
+      <c r="D600">
+        <v>4.9372770640562882</v>
+      </c>
+      <c r="E600">
+        <v>-10.638640338865869</v>
+      </c>
+      <c r="F600" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G600" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A601" t="s">
+        <v>532</v>
+      </c>
+      <c r="B601" t="s">
+        <v>569</v>
+      </c>
+      <c r="C601" t="s">
+        <v>703</v>
+      </c>
+      <c r="D601">
+        <v>6.0250401742375139</v>
+      </c>
+      <c r="E601">
+        <v>-11.550474276486101</v>
+      </c>
+      <c r="F601" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G601" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A602" t="s">
+        <v>532</v>
+      </c>
+      <c r="B602" t="s">
+        <v>570</v>
+      </c>
+      <c r="C602" t="s">
+        <v>703</v>
+      </c>
+      <c r="D602">
+        <v>8.0741541884919421</v>
+      </c>
+      <c r="E602">
+        <v>-12.323407323449066</v>
+      </c>
+      <c r="F602" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G602" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A603" t="s">
+        <v>532</v>
+      </c>
+      <c r="B603" t="s">
+        <v>571</v>
+      </c>
+      <c r="C603" t="s">
+        <v>703</v>
+      </c>
+      <c r="D603">
+        <v>7.6521127508037701</v>
+      </c>
+      <c r="E603">
+        <v>-12.769623833240999</v>
+      </c>
+      <c r="F603" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G603" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A604" t="s">
+        <v>532</v>
+      </c>
+      <c r="B604" t="s">
+        <v>572</v>
+      </c>
+      <c r="C604" t="s">
+        <v>703</v>
+      </c>
+      <c r="D604">
+        <v>9.2250181455628937</v>
+      </c>
+      <c r="E604">
+        <v>-12.789210189279109</v>
+      </c>
+      <c r="F604" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G604" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="605" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A605" t="s">
+        <v>532</v>
+      </c>
+      <c r="B605" t="s">
+        <v>573</v>
+      </c>
+      <c r="C605" t="s">
+        <v>703</v>
+      </c>
+      <c r="D605">
+        <v>5.70256128371242</v>
+      </c>
+      <c r="E605">
+        <v>190.48014309715978</v>
+      </c>
+      <c r="F605" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G605" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="606" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A606" t="s">
+        <v>532</v>
+      </c>
+      <c r="B606" t="s">
+        <v>574</v>
+      </c>
+      <c r="C606" t="s">
+        <v>703</v>
+      </c>
+      <c r="D606">
+        <v>2.2854769741321741</v>
+      </c>
+      <c r="E606">
+        <v>-17.031415570470223</v>
+      </c>
+      <c r="F606" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G606" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A607" t="s">
+        <v>532</v>
+      </c>
+      <c r="B607" t="s">
+        <v>575</v>
+      </c>
+      <c r="C607" t="s">
+        <v>703</v>
+      </c>
+      <c r="D607">
+        <v>2.9808744345432081</v>
+      </c>
+      <c r="E607">
+        <v>-7.4896675414663889</v>
+      </c>
+      <c r="F607" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G607" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A608" t="s">
+        <v>532</v>
+      </c>
+      <c r="B608" t="s">
+        <v>576</v>
+      </c>
+      <c r="C608" t="s">
+        <v>703</v>
+      </c>
+      <c r="D608">
+        <v>2.8449014167948157</v>
+      </c>
+      <c r="E608">
+        <v>-10.674219362778832</v>
+      </c>
+      <c r="F608" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G608" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A609" t="s">
+        <v>532</v>
+      </c>
+      <c r="B609" t="s">
+        <v>577</v>
+      </c>
+      <c r="C609" t="s">
+        <v>703</v>
+      </c>
+      <c r="D609">
+        <v>3.7101895089048793</v>
+      </c>
+      <c r="E609">
+        <v>-10.164912969631597</v>
+      </c>
+      <c r="F609" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G609" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="610" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A610" t="s">
+        <v>532</v>
+      </c>
+      <c r="B610" t="s">
+        <v>578</v>
+      </c>
+      <c r="C610" t="s">
+        <v>703</v>
+      </c>
+      <c r="D610">
+        <v>4.6973228864143444</v>
+      </c>
+      <c r="E610">
+        <v>-10.52666981615481</v>
+      </c>
+      <c r="F610" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G610" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A611" t="s">
+        <v>532</v>
+      </c>
+      <c r="B611" t="s">
+        <v>579</v>
+      </c>
+      <c r="C611" t="s">
+        <v>703</v>
+      </c>
+      <c r="D611">
+        <v>4.3797478050977254</v>
+      </c>
+      <c r="E611">
+        <v>-13.498592585081807</v>
+      </c>
+      <c r="F611" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G611" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="612" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A612" t="s">
+        <v>532</v>
+      </c>
+      <c r="B612" t="s">
+        <v>580</v>
+      </c>
+      <c r="C612" t="s">
+        <v>703</v>
+      </c>
+      <c r="D612">
+        <v>6.6755561203179141</v>
+      </c>
+      <c r="E612">
+        <v>-13.716585649188449</v>
+      </c>
+      <c r="F612" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G612" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A613" t="s">
+        <v>532</v>
+      </c>
+      <c r="B613" t="s">
+        <v>581</v>
+      </c>
+      <c r="C613" t="s">
+        <v>703</v>
+      </c>
+      <c r="D613">
+        <v>4.1073784233723014</v>
+      </c>
+      <c r="E613">
+        <v>-15.459453442239916</v>
+      </c>
+      <c r="F613" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G613" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="614" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A614" t="s">
+        <v>532</v>
+      </c>
+      <c r="B614" t="s">
+        <v>582</v>
+      </c>
+      <c r="C614" t="s">
+        <v>703</v>
+      </c>
+      <c r="D614">
+        <v>4.4977178585431679</v>
+      </c>
+      <c r="E614">
+        <v>-15.850842738370467</v>
+      </c>
+      <c r="F614" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G614" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="615" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A615" t="s">
+        <v>532</v>
+      </c>
+      <c r="B615" t="s">
+        <v>583</v>
+      </c>
+      <c r="C615" t="s">
+        <v>703</v>
+      </c>
+      <c r="D615">
+        <v>4.6148791849344288</v>
+      </c>
+      <c r="E615">
+        <v>-5.5458261873803885</v>
+      </c>
+      <c r="F615" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G615" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="616" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A616" t="s">
+        <v>532</v>
+      </c>
+      <c r="B616" t="s">
+        <v>584</v>
+      </c>
+      <c r="C616" t="s">
+        <v>703</v>
+      </c>
+      <c r="D616">
+        <v>0.78762390203477772</v>
+      </c>
+      <c r="E616">
+        <v>294.78252361508856</v>
+      </c>
+      <c r="F616" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G616" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A617" t="s">
+        <v>532</v>
+      </c>
+      <c r="B617" t="s">
+        <v>585</v>
+      </c>
+      <c r="C617" t="s">
+        <v>703</v>
+      </c>
+      <c r="D617">
+        <v>0.22400463226195338</v>
+      </c>
+      <c r="E617">
+        <v>-0.42231470113746639</v>
+      </c>
+      <c r="F617" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G617" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="618" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A618" t="s">
+        <v>532</v>
+      </c>
+      <c r="B618" t="s">
+        <v>586</v>
+      </c>
+      <c r="C618" t="s">
+        <v>703</v>
+      </c>
+      <c r="D618">
+        <v>0.1240081048042863</v>
+      </c>
+      <c r="E618">
+        <v>11.90489210331106</v>
+      </c>
+      <c r="F618" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G618" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="619" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A619" t="s">
+        <v>532</v>
+      </c>
+      <c r="B619" t="s">
+        <v>587</v>
+      </c>
+      <c r="C619" t="s">
+        <v>703</v>
+      </c>
+      <c r="D619">
+        <v>0.10416518125775354</v>
+      </c>
+      <c r="E619">
+        <v>12.19605267900597</v>
+      </c>
+      <c r="F619" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G619" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="620" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A620" t="s">
+        <v>532</v>
+      </c>
+      <c r="B620" t="s">
+        <v>588</v>
+      </c>
+      <c r="C620" t="s">
+        <v>703</v>
+      </c>
+      <c r="D620">
+        <v>0.10851643826156701</v>
+      </c>
+      <c r="E620">
+        <v>12.509932401244008</v>
+      </c>
+      <c r="F620" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G620" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="621" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A621" t="s">
+        <v>532</v>
+      </c>
+      <c r="B621" t="s">
+        <v>589</v>
+      </c>
+      <c r="C621" t="s">
+        <v>703</v>
+      </c>
+      <c r="D621">
+        <v>0.11422401490048062</v>
+      </c>
+      <c r="E621">
+        <v>11.260223833207682</v>
+      </c>
+      <c r="F621" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G621" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="622" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A622" t="s">
+        <v>532</v>
+      </c>
+      <c r="B622" t="s">
+        <v>590</v>
+      </c>
+      <c r="C622" t="s">
+        <v>703</v>
+      </c>
+      <c r="D622">
+        <v>0.16482429609016855</v>
+      </c>
+      <c r="E622">
+        <v>5.5638443315346251</v>
+      </c>
+      <c r="F622" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G622" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="623" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A623" t="s">
+        <v>532</v>
+      </c>
+      <c r="B623" t="s">
+        <v>591</v>
+      </c>
+      <c r="C623" t="s">
+        <v>703</v>
+      </c>
+      <c r="D623">
+        <v>0.22311719590037568</v>
+      </c>
+      <c r="E623">
+        <v>5.6115526244335925</v>
+      </c>
+      <c r="F623" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G623" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="624" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A624" t="s">
+        <v>532</v>
+      </c>
+      <c r="B624" t="s">
+        <v>592</v>
+      </c>
+      <c r="C624" t="s">
+        <v>703</v>
+      </c>
+      <c r="D624">
+        <v>0.32285200789697982</v>
+      </c>
+      <c r="E624">
+        <v>2.7084054622318945</v>
+      </c>
+      <c r="F624" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G624" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A625" t="s">
+        <v>532</v>
+      </c>
+      <c r="B625" t="s">
+        <v>593</v>
+      </c>
+      <c r="C625" t="s">
+        <v>703</v>
+      </c>
+      <c r="D625">
+        <v>0.14110845716102402</v>
+      </c>
+      <c r="E625">
+        <v>11.603982582850364</v>
+      </c>
+      <c r="F625" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G625" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A626" t="s">
+        <v>532</v>
+      </c>
+      <c r="B626" t="s">
+        <v>594</v>
+      </c>
+      <c r="C626" t="s">
+        <v>703</v>
+      </c>
+      <c r="D626">
+        <v>0.25931917512292996</v>
+      </c>
+      <c r="E626">
+        <v>332.72198744120942</v>
+      </c>
+      <c r="F626" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G626" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A627" t="s">
+        <v>532</v>
+      </c>
+      <c r="B627" t="s">
+        <v>595</v>
+      </c>
+      <c r="C627" t="s">
+        <v>703</v>
+      </c>
+      <c r="D627">
+        <v>0.14909684437175452</v>
+      </c>
+      <c r="E627">
+        <v>8.8291642058945534</v>
+      </c>
+      <c r="F627" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G627" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A628" t="s">
+        <v>532</v>
+      </c>
+      <c r="B628" t="s">
+        <v>596</v>
+      </c>
+      <c r="C628" t="s">
+        <v>703</v>
+      </c>
+      <c r="D628">
+        <v>0.14712197903290031</v>
+      </c>
+      <c r="E628">
+        <v>3.5460226218309892</v>
+      </c>
+      <c r="F628" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G628" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A629" t="s">
+        <v>532</v>
+      </c>
+      <c r="B629" t="s">
+        <v>597</v>
+      </c>
+      <c r="C629" t="s">
+        <v>703</v>
+      </c>
+      <c r="D629">
+        <v>9.6707327771786519E-2</v>
+      </c>
+      <c r="E629">
+        <v>3.2284692082542144</v>
+      </c>
+      <c r="F629" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G629" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A630" t="s">
+        <v>532</v>
+      </c>
+      <c r="B630" t="s">
+        <v>598</v>
+      </c>
+      <c r="C630" t="s">
+        <v>703</v>
+      </c>
+      <c r="D630">
+        <v>0.11008262782541318</v>
+      </c>
+      <c r="E630">
+        <v>1.9280167430378263</v>
+      </c>
+      <c r="F630" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G630" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="631" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A631" t="s">
+        <v>532</v>
+      </c>
+      <c r="B631" t="s">
+        <v>599</v>
+      </c>
+      <c r="C631" t="s">
+        <v>703</v>
+      </c>
+      <c r="D631">
+        <v>0.13464375956146224</v>
+      </c>
+      <c r="E631">
+        <v>1.1005218910821561</v>
+      </c>
+      <c r="F631" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G631" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A632" t="s">
+        <v>532</v>
+      </c>
+      <c r="B632" t="s">
+        <v>600</v>
+      </c>
+      <c r="C632" t="s">
+        <v>703</v>
+      </c>
+      <c r="D632">
+        <v>0.1436133762763698</v>
+      </c>
+      <c r="E632">
+        <v>-0.18016693734557521</v>
+      </c>
+      <c r="F632" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G632" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="633" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A633" t="s">
+        <v>532</v>
+      </c>
+      <c r="B633" t="s">
+        <v>601</v>
+      </c>
+      <c r="C633" t="s">
+        <v>703</v>
+      </c>
+      <c r="D633">
+        <v>0.13691744788775173</v>
+      </c>
+      <c r="E633">
+        <v>1.8819971511704949</v>
+      </c>
+      <c r="F633" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G633" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A634" t="s">
+        <v>532</v>
+      </c>
+      <c r="B634" t="s">
+        <v>602</v>
+      </c>
+      <c r="C634" t="s">
+        <v>703</v>
+      </c>
+      <c r="D634">
+        <v>0.13451089383590845</v>
+      </c>
+      <c r="E634">
+        <v>4.5967831339075254</v>
+      </c>
+      <c r="F634" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G634" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A635" t="s">
+        <v>532</v>
+      </c>
+      <c r="B635" t="s">
+        <v>603</v>
+      </c>
+      <c r="C635" t="s">
+        <v>703</v>
+      </c>
+      <c r="D635">
+        <v>0.14209658027672012</v>
+      </c>
+      <c r="E635">
+        <v>6.8658630284613444</v>
+      </c>
+      <c r="F635" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G635" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="636" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A636" t="s">
+        <v>532</v>
+      </c>
+      <c r="B636" t="s">
+        <v>505</v>
+      </c>
+      <c r="C636" t="s">
+        <v>703</v>
+      </c>
+      <c r="D636">
+        <v>3.8295760264473224</v>
+      </c>
+      <c r="E636">
+        <v>19.863812603377074</v>
+      </c>
+      <c r="F636" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G636" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="637" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A637" t="s">
+        <v>532</v>
+      </c>
+      <c r="B637" t="s">
+        <v>604</v>
+      </c>
+      <c r="C637" t="s">
+        <v>703</v>
+      </c>
+      <c r="D637">
+        <v>7.8163991550331753</v>
+      </c>
+      <c r="E637">
+        <v>61.827733755542468</v>
+      </c>
+      <c r="F637" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G637" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="638" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A638" t="s">
+        <v>532</v>
+      </c>
+      <c r="B638" t="s">
+        <v>605</v>
+      </c>
+      <c r="C638" t="s">
+        <v>703</v>
+      </c>
+      <c r="D638">
+        <v>2.3851119532800955</v>
+      </c>
+      <c r="E638">
+        <v>-15.343411967639669</v>
+      </c>
+      <c r="F638" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G638" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A639" t="s">
+        <v>532</v>
+      </c>
+      <c r="B639" t="s">
+        <v>606</v>
+      </c>
+      <c r="C639" t="s">
+        <v>703</v>
+      </c>
+      <c r="D639">
+        <v>7.5389997638553901</v>
+      </c>
+      <c r="E639">
+        <v>3.5983269292179791</v>
+      </c>
+      <c r="F639" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G639" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="640" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A640" t="s">
+        <v>532</v>
+      </c>
+      <c r="B640" t="s">
+        <v>607</v>
+      </c>
+      <c r="C640" t="s">
+        <v>703</v>
+      </c>
+      <c r="D640">
+        <v>5.459475676289328</v>
+      </c>
+      <c r="E640">
+        <v>-3.0212842592113809</v>
+      </c>
+      <c r="F640" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G640" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="641" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A641" t="s">
+        <v>532</v>
+      </c>
+      <c r="B641" t="s">
+        <v>608</v>
+      </c>
+      <c r="C641" t="s">
+        <v>703</v>
+      </c>
+      <c r="D641">
+        <v>4.524563971368635</v>
+      </c>
+      <c r="E641">
+        <v>-9.3731304841682537</v>
+      </c>
+      <c r="F641" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G641" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="642" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A642" t="s">
+        <v>532</v>
+      </c>
+      <c r="B642" t="s">
+        <v>609</v>
+      </c>
+      <c r="C642" t="s">
+        <v>703</v>
+      </c>
+      <c r="D642">
+        <v>3.7444897293663333</v>
+      </c>
+      <c r="E642">
+        <v>-11.865952663064466</v>
+      </c>
+      <c r="F642" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G642" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="643" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A643" t="s">
+        <v>532</v>
+      </c>
+      <c r="B643" t="s">
+        <v>610</v>
+      </c>
+      <c r="C643" t="s">
+        <v>703</v>
+      </c>
+      <c r="D643">
+        <v>5.4265168921269433</v>
+      </c>
+      <c r="E643">
+        <v>-10.440884571405768</v>
+      </c>
+      <c r="F643" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G643" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="644" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A644" t="s">
+        <v>532</v>
+      </c>
+      <c r="B644" t="s">
+        <v>611</v>
+      </c>
+      <c r="C644" t="s">
+        <v>703</v>
+      </c>
+      <c r="D644">
+        <v>5.6359300749971295</v>
+      </c>
+      <c r="E644">
+        <v>-12.146329556579712</v>
+      </c>
+      <c r="F644" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G644" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="645" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A645" t="s">
+        <v>532</v>
+      </c>
+      <c r="B645" t="s">
+        <v>612</v>
+      </c>
+      <c r="C645" t="s">
+        <v>703</v>
+      </c>
+      <c r="D645">
+        <v>3.8899454083345981</v>
+      </c>
+      <c r="E645">
+        <v>-12.233350914371661</v>
+      </c>
+      <c r="F645" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G645" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="646" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A646" t="s">
+        <v>532</v>
+      </c>
+      <c r="B646" t="s">
+        <v>613</v>
+      </c>
+      <c r="C646" t="s">
+        <v>703</v>
+      </c>
+      <c r="D646">
+        <v>2.7820684646279354</v>
+      </c>
+      <c r="E646">
+        <v>-13.344561752614842</v>
+      </c>
+      <c r="F646" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G646" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="647" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A647" t="s">
+        <v>532</v>
+      </c>
+      <c r="B647" t="s">
+        <v>614</v>
+      </c>
+      <c r="C647" t="s">
+        <v>703</v>
+      </c>
+      <c r="D647">
+        <v>0.48043504249005015</v>
+      </c>
+      <c r="E647">
+        <v>273.50967971187265</v>
+      </c>
+      <c r="F647" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G647" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="648" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A648" t="s">
+        <v>532</v>
+      </c>
+      <c r="B648" t="s">
+        <v>615</v>
+      </c>
+      <c r="C648" t="s">
+        <v>703</v>
+      </c>
+      <c r="D648">
+        <v>0.1384132623992223</v>
+      </c>
+      <c r="E648">
+        <v>2.0716550054790908</v>
+      </c>
+      <c r="F648" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G648" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="649" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A649" t="s">
+        <v>532</v>
+      </c>
+      <c r="B649" t="s">
+        <v>616</v>
+      </c>
+      <c r="C649" t="s">
+        <v>703</v>
+      </c>
+      <c r="D649">
+        <v>0.22918022018437703</v>
+      </c>
+      <c r="E649">
+        <v>-0.29606616185621704</v>
+      </c>
+      <c r="F649" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G649" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="650" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A650" t="s">
+        <v>532</v>
+      </c>
+      <c r="B650" t="s">
+        <v>617</v>
+      </c>
+      <c r="C650" t="s">
+        <v>703</v>
+      </c>
+      <c r="D650">
+        <v>0.24732492283292637</v>
+      </c>
+      <c r="E650">
+        <v>-2.2441998690837934</v>
+      </c>
+      <c r="F650" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G650" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="651" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A651" t="s">
+        <v>532</v>
+      </c>
+      <c r="B651" t="s">
+        <v>618</v>
+      </c>
+      <c r="C651" t="s">
+        <v>703</v>
+      </c>
+      <c r="D651">
+        <v>0.23066362065565826</v>
+      </c>
+      <c r="E651">
+        <v>-4.5542912585842217</v>
+      </c>
+      <c r="F651" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G651" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="652" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A652" t="s">
+        <v>532</v>
+      </c>
+      <c r="B652" t="s">
+        <v>619</v>
+      </c>
+      <c r="C652" t="s">
+        <v>703</v>
+      </c>
+      <c r="D652">
+        <v>0.14385304313887184</v>
+      </c>
+      <c r="E652">
+        <v>-2.4847279412025252</v>
+      </c>
+      <c r="F652" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G652" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="653" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A653" t="s">
+        <v>532</v>
+      </c>
+      <c r="B653" t="s">
+        <v>620</v>
+      </c>
+      <c r="C653" t="s">
+        <v>703</v>
+      </c>
+      <c r="D653">
+        <v>0.14991515666098504</v>
+      </c>
+      <c r="E653">
+        <v>-0.97294405284282703</v>
+      </c>
+      <c r="F653" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G653" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="654" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A654" t="s">
+        <v>532</v>
+      </c>
+      <c r="B654" t="s">
+        <v>621</v>
+      </c>
+      <c r="C654" t="s">
+        <v>703</v>
+      </c>
+      <c r="D654">
+        <v>0.14029180494540119</v>
+      </c>
+      <c r="E654">
+        <v>1.1903526611551811</v>
+      </c>
+      <c r="F654" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G654" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="655" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A655" t="s">
+        <v>532</v>
+      </c>
+      <c r="B655" t="s">
+        <v>622</v>
+      </c>
+      <c r="C655" t="s">
+        <v>703</v>
+      </c>
+      <c r="D655">
+        <v>0.13530521791829006</v>
+      </c>
+      <c r="E655">
+        <v>2.6751100420198952</v>
+      </c>
+      <c r="F655" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G655" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="656" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A656" t="s">
+        <v>532</v>
+      </c>
+      <c r="B656" t="s">
+        <v>623</v>
+      </c>
+      <c r="C656" t="s">
+        <v>703</v>
+      </c>
+      <c r="D656">
+        <v>0.1556979484749719</v>
+      </c>
+      <c r="E656">
+        <v>6.0854566230646405</v>
+      </c>
+      <c r="F656" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G656" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="657" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A657" t="s">
+        <v>532</v>
+      </c>
+      <c r="B657" t="s">
+        <v>624</v>
+      </c>
+      <c r="C657" t="s">
+        <v>703</v>
+      </c>
+      <c r="D657">
+        <v>12.421096209715268</v>
+      </c>
+      <c r="E657">
+        <v>300.54293092303112</v>
+      </c>
+      <c r="F657" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G657" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A658" t="s">
+        <v>532</v>
+      </c>
+      <c r="B658" t="s">
+        <v>625</v>
+      </c>
+      <c r="C658" t="s">
+        <v>703</v>
+      </c>
+      <c r="D658">
+        <v>2.8282140552229622</v>
+      </c>
+      <c r="E658">
+        <v>-11.746752777810743</v>
+      </c>
+      <c r="F658" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G658" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="659" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A659" t="s">
+        <v>532</v>
+      </c>
+      <c r="B659" t="s">
+        <v>626</v>
+      </c>
+      <c r="C659" t="s">
+        <v>703</v>
+      </c>
+      <c r="D659">
+        <v>5.893895129477043</v>
+      </c>
+      <c r="E659">
+        <v>67.692674265474636</v>
+      </c>
+      <c r="F659" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G659" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="660" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A660" t="s">
+        <v>532</v>
+      </c>
+      <c r="B660" t="s">
+        <v>627</v>
+      </c>
+      <c r="C660" t="s">
+        <v>703</v>
+      </c>
+      <c r="D660">
+        <v>8.1370113666725565</v>
+      </c>
+      <c r="E660">
+        <v>3.2383138917530907</v>
+      </c>
+      <c r="F660" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G660" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A661" t="s">
+        <v>532</v>
+      </c>
+      <c r="B661" t="s">
+        <v>628</v>
+      </c>
+      <c r="C661" t="s">
+        <v>703</v>
+      </c>
+      <c r="D661">
+        <v>6.1826846523279837</v>
+      </c>
+      <c r="E661">
+        <v>9.5564389624751556E-2</v>
+      </c>
+      <c r="F661" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G661" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="662" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A662" t="s">
+        <v>532</v>
+      </c>
+      <c r="B662" t="s">
+        <v>629</v>
+      </c>
+      <c r="C662" t="s">
+        <v>703</v>
+      </c>
+      <c r="D662">
+        <v>6.1784839437993702</v>
+      </c>
+      <c r="E662">
+        <v>-1.9637990281779381</v>
+      </c>
+      <c r="F662" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G662" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="663" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A663" t="s">
+        <v>532</v>
+      </c>
+      <c r="B663" t="s">
+        <v>630</v>
+      </c>
+      <c r="C663" t="s">
+        <v>703</v>
+      </c>
+      <c r="D663">
+        <v>5.9073811603246682</v>
+      </c>
+      <c r="E663">
+        <v>-4.0583250377016</v>
+      </c>
+      <c r="F663" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G663" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="664" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A664" t="s">
+        <v>532</v>
+      </c>
+      <c r="B664" t="s">
+        <v>631</v>
+      </c>
+      <c r="C664" t="s">
+        <v>703</v>
+      </c>
+      <c r="D664">
+        <v>4.7144133066911174</v>
+      </c>
+      <c r="E664">
+        <v>-6.712611277136336</v>
+      </c>
+      <c r="F664" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G664" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="665" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A665" t="s">
+        <v>532</v>
+      </c>
+      <c r="B665" t="s">
+        <v>632</v>
+      </c>
+      <c r="C665" t="s">
+        <v>703</v>
+      </c>
+      <c r="D665">
+        <v>4.3253439595563234</v>
+      </c>
+      <c r="E665">
+        <v>-7.32414960422485</v>
+      </c>
+      <c r="F665" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G665" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="666" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A666" t="s">
+        <v>532</v>
+      </c>
+      <c r="B666" t="s">
+        <v>633</v>
+      </c>
+      <c r="C666" t="s">
+        <v>703</v>
+      </c>
+      <c r="D666">
+        <v>4.0131361477091652</v>
+      </c>
+      <c r="E666">
+        <v>-9.9747993400983432</v>
+      </c>
+      <c r="F666" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G666" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="667" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A667" t="s">
+        <v>532</v>
+      </c>
+      <c r="B667" t="s">
+        <v>634</v>
+      </c>
+      <c r="C667" t="s">
+        <v>703</v>
+      </c>
+      <c r="D667">
+        <v>1.6597713935387715</v>
+      </c>
+      <c r="E667">
+        <v>316.12400897190105</v>
+      </c>
+      <c r="F667" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G667" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A668" t="s">
+        <v>532</v>
+      </c>
+      <c r="B668" t="s">
+        <v>635</v>
+      </c>
+      <c r="C668" t="s">
+        <v>703</v>
+      </c>
+      <c r="D668">
+        <v>9.0829432503142224E-2</v>
+      </c>
+      <c r="E668">
+        <v>9.2510891844734005</v>
+      </c>
+      <c r="F668" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G668" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="669" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A669" t="s">
+        <v>532</v>
+      </c>
+      <c r="B669" t="s">
+        <v>636</v>
+      </c>
+      <c r="C669" t="s">
+        <v>703</v>
+      </c>
+      <c r="D669">
+        <v>0.1518328841662005</v>
+      </c>
+      <c r="E669">
+        <v>9.1089115962216702</v>
+      </c>
+      <c r="F669" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G669" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="670" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A670" t="s">
+        <v>532</v>
+      </c>
+      <c r="B670" t="s">
+        <v>637</v>
+      </c>
+      <c r="C670" t="s">
+        <v>703</v>
+      </c>
+      <c r="D670">
+        <v>0.10467921949268441</v>
+      </c>
+      <c r="E670">
+        <v>8.7401573286130869</v>
+      </c>
+      <c r="F670" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G670" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="671" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A671" t="s">
+        <v>532</v>
+      </c>
+      <c r="B671" t="s">
+        <v>638</v>
+      </c>
+      <c r="C671" t="s">
+        <v>703</v>
+      </c>
+      <c r="D671">
+        <v>9.6041026460205542E-2</v>
+      </c>
+      <c r="E671">
+        <v>8.0071044892774808</v>
+      </c>
+      <c r="F671" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G671" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="672" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A672" t="s">
+        <v>532</v>
+      </c>
+      <c r="B672" t="s">
+        <v>639</v>
+      </c>
+      <c r="C672" t="s">
+        <v>703</v>
+      </c>
+      <c r="D672">
+        <v>9.2642146855781982E-2</v>
+      </c>
+      <c r="E672">
+        <v>8.7110153476082814</v>
+      </c>
+      <c r="F672" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G672" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="673" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A673" t="s">
+        <v>532</v>
+      </c>
+      <c r="B673" t="s">
+        <v>640</v>
+      </c>
+      <c r="C673" t="s">
+        <v>703</v>
+      </c>
+      <c r="D673">
+        <v>0.11230673521767125</v>
+      </c>
+      <c r="E673">
+        <v>4.591591281700282</v>
+      </c>
+      <c r="F673" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G673" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="674" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A674" t="s">
+        <v>532</v>
+      </c>
+      <c r="B674" t="s">
+        <v>641</v>
+      </c>
+      <c r="C674" t="s">
+        <v>703</v>
+      </c>
+      <c r="D674">
+        <v>0.10299014193961807</v>
+      </c>
+      <c r="E674">
+        <v>6.8056702795084689</v>
+      </c>
+      <c r="F674" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G674" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="675" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A675" t="s">
+        <v>532</v>
+      </c>
+      <c r="B675" t="s">
+        <v>642</v>
+      </c>
+      <c r="C675" t="s">
+        <v>703</v>
+      </c>
+      <c r="D675">
+        <v>0.1102492152502955</v>
+      </c>
+      <c r="E675">
+        <v>0.86185448423580979</v>
+      </c>
+      <c r="F675" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G675" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="676" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A676" t="s">
+        <v>532</v>
+      </c>
+      <c r="B676" t="s">
+        <v>643</v>
+      </c>
+      <c r="C676" t="s">
+        <v>703</v>
+      </c>
+      <c r="D676">
+        <v>8.7598805699072871E-2</v>
+      </c>
+      <c r="E676">
+        <v>7.9065400194362425</v>
+      </c>
+      <c r="F676" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G676" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="677" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A677" t="s">
+        <v>532</v>
+      </c>
+      <c r="B677" t="s">
+        <v>644</v>
+      </c>
+      <c r="C677" t="s">
+        <v>703</v>
+      </c>
+      <c r="D677">
+        <v>13.054771143857192</v>
+      </c>
+      <c r="E677">
+        <v>166.17738178346332</v>
+      </c>
+      <c r="F677" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G677" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A678" t="s">
+        <v>532</v>
+      </c>
+      <c r="B678" t="s">
+        <v>645</v>
+      </c>
+      <c r="C678" t="s">
+        <v>703</v>
+      </c>
+      <c r="D678">
+        <v>4.8973020313621305</v>
+      </c>
+      <c r="E678">
+        <v>-15.159687399890075</v>
+      </c>
+      <c r="F678" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G678" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="679" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A679" t="s">
+        <v>532</v>
+      </c>
+      <c r="B679" t="s">
+        <v>646</v>
+      </c>
+      <c r="C679" t="s">
+        <v>703</v>
+      </c>
+      <c r="D679">
+        <v>6.6425822429546058</v>
+      </c>
+      <c r="E679">
+        <v>-2.8466014692586725</v>
+      </c>
+      <c r="F679" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G679" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="680" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A680" t="s">
+        <v>532</v>
+      </c>
+      <c r="B680" t="s">
+        <v>647</v>
+      </c>
+      <c r="C680" t="s">
+        <v>703</v>
+      </c>
+      <c r="D680">
+        <v>7.0720763508345454</v>
+      </c>
+      <c r="E680">
+        <v>-8.9519676618574202</v>
+      </c>
+      <c r="F680" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G680" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="681" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A681" t="s">
+        <v>532</v>
+      </c>
+      <c r="B681" t="s">
+        <v>648</v>
+      </c>
+      <c r="C681" t="s">
+        <v>703</v>
+      </c>
+      <c r="D681">
+        <v>5.5414169546611216</v>
+      </c>
+      <c r="E681">
+        <v>-8.9427463057539498</v>
+      </c>
+      <c r="F681" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G681" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="682" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A682" t="s">
+        <v>532</v>
+      </c>
+      <c r="B682" t="s">
+        <v>649</v>
+      </c>
+      <c r="C682" t="s">
+        <v>703</v>
+      </c>
+      <c r="D682">
+        <v>7.1230486990779207</v>
+      </c>
+      <c r="E682">
+        <v>-10.838872288564149</v>
+      </c>
+      <c r="F682" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G682" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A683" t="s">
+        <v>532</v>
+      </c>
+      <c r="B683" t="s">
+        <v>650</v>
+      </c>
+      <c r="C683" t="s">
+        <v>703</v>
+      </c>
+      <c r="D683">
+        <v>9.0350968913606593</v>
+      </c>
+      <c r="E683">
+        <v>-13.34343073843076</v>
+      </c>
+      <c r="F683" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G683" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="684" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A684" t="s">
+        <v>532</v>
+      </c>
+      <c r="B684" t="s">
+        <v>651</v>
+      </c>
+      <c r="C684" t="s">
+        <v>703</v>
+      </c>
+      <c r="D684">
+        <v>11.043423584260232</v>
+      </c>
+      <c r="E684">
+        <v>-13.815999543510728</v>
+      </c>
+      <c r="F684" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G684" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A685" t="s">
+        <v>532</v>
+      </c>
+      <c r="B685" t="s">
+        <v>652</v>
+      </c>
+      <c r="C685" t="s">
+        <v>703</v>
+      </c>
+      <c r="D685">
+        <v>12.087577174744599</v>
+      </c>
+      <c r="E685">
+        <v>-13.997608423542237</v>
+      </c>
+      <c r="F685" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G685" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A686" t="s">
+        <v>532</v>
+      </c>
+      <c r="B686" t="s">
+        <v>653</v>
+      </c>
+      <c r="C686" t="s">
+        <v>703</v>
+      </c>
+      <c r="D686">
+        <v>9.5054649524655996</v>
+      </c>
+      <c r="E686">
+        <v>-14.637642919303314</v>
+      </c>
+      <c r="F686" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G686" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A687" t="s">
+        <v>532</v>
+      </c>
+      <c r="B687" t="s">
+        <v>654</v>
+      </c>
+      <c r="C687" t="s">
+        <v>703</v>
+      </c>
+      <c r="D687">
+        <v>0.8831848785264248</v>
+      </c>
+      <c r="E687">
+        <v>357.0133405932084</v>
+      </c>
+      <c r="F687" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G687" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="688" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A688" t="s">
+        <v>532</v>
+      </c>
+      <c r="B688" t="s">
+        <v>655</v>
+      </c>
+      <c r="C688" t="s">
+        <v>703</v>
+      </c>
+      <c r="D688">
+        <v>0.12135985832976187</v>
+      </c>
+      <c r="E688">
+        <v>5.275642470213505</v>
+      </c>
+      <c r="F688" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G688" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="689" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A689" t="s">
+        <v>532</v>
+      </c>
+      <c r="B689" t="s">
+        <v>656</v>
+      </c>
+      <c r="C689" t="s">
+        <v>703</v>
+      </c>
+      <c r="D689">
+        <v>0.20143365326610574</v>
+      </c>
+      <c r="E689">
+        <v>-1.0600545697913795</v>
+      </c>
+      <c r="F689" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G689" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="690" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A690" t="s">
+        <v>532</v>
+      </c>
+      <c r="B690" t="s">
+        <v>657</v>
+      </c>
+      <c r="C690" t="s">
+        <v>703</v>
+      </c>
+      <c r="D690">
+        <v>0.21366584895962237</v>
+      </c>
+      <c r="E690">
+        <v>-2.7601296074863164</v>
+      </c>
+      <c r="F690" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G690" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="691" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A691" t="s">
+        <v>532</v>
+      </c>
+      <c r="B691" t="s">
+        <v>658</v>
+      </c>
+      <c r="C691" t="s">
+        <v>703</v>
+      </c>
+      <c r="D691">
+        <v>0.18450019238284382</v>
+      </c>
+      <c r="E691">
+        <v>-6.5610124272022006</v>
+      </c>
+      <c r="F691" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G691" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="692" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A692" t="s">
+        <v>532</v>
+      </c>
+      <c r="B692" t="s">
+        <v>659</v>
+      </c>
+      <c r="C692" t="s">
+        <v>703</v>
+      </c>
+      <c r="D692">
+        <v>0.23952103546343748</v>
+      </c>
+      <c r="E692">
+        <v>-7.1163465448869729</v>
+      </c>
+      <c r="F692" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G692" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="693" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A693" t="s">
+        <v>532</v>
+      </c>
+      <c r="B693" t="s">
+        <v>660</v>
+      </c>
+      <c r="C693" t="s">
+        <v>703</v>
+      </c>
+      <c r="D693">
+        <v>0.14425561965412359</v>
+      </c>
+      <c r="E693">
+        <v>-6.6413374369791498</v>
+      </c>
+      <c r="F693" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G693" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="694" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A694" t="s">
+        <v>532</v>
+      </c>
+      <c r="B694" t="s">
+        <v>661</v>
+      </c>
+      <c r="C694" t="s">
+        <v>703</v>
+      </c>
+      <c r="D694">
+        <v>0.12628287693343096</v>
+      </c>
+      <c r="E694">
+        <v>-4.0856555080855976</v>
+      </c>
+      <c r="F694" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G694" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="695" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A695" t="s">
+        <v>532</v>
+      </c>
+      <c r="B695" t="s">
+        <v>662</v>
+      </c>
+      <c r="C695" t="s">
+        <v>703</v>
+      </c>
+      <c r="D695">
+        <v>0.13479477695952252</v>
+      </c>
+      <c r="E695">
+        <v>-0.79553325646009654</v>
+      </c>
+      <c r="F695" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G695" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="696" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A696" t="s">
+        <v>532</v>
+      </c>
+      <c r="B696" t="s">
+        <v>663</v>
+      </c>
+      <c r="C696" t="s">
+        <v>703</v>
+      </c>
+      <c r="D696">
+        <v>0.10961890362820746</v>
+      </c>
+      <c r="E696">
+        <v>-3.1638749151248646E-2</v>
+      </c>
+      <c r="F696" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G696" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="697" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A697" t="s">
+        <v>532</v>
+      </c>
+      <c r="B697" t="s">
+        <v>664</v>
+      </c>
+      <c r="C697" t="s">
+        <v>703</v>
+      </c>
+      <c r="D697">
+        <v>6.5777437325637029</v>
+      </c>
+      <c r="E697">
+        <v>205.05584552356925</v>
+      </c>
+      <c r="F697" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G697" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="698" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A698" t="s">
+        <v>532</v>
+      </c>
+      <c r="B698" t="s">
+        <v>665</v>
+      </c>
+      <c r="C698" t="s">
+        <v>703</v>
+      </c>
+      <c r="D698">
+        <v>4.1254389294919873</v>
+      </c>
+      <c r="E698">
+        <v>-15.31127244233344</v>
+      </c>
+      <c r="F698" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G698" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="699" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A699" t="s">
+        <v>532</v>
+      </c>
+      <c r="B699" t="s">
+        <v>666</v>
+      </c>
+      <c r="C699" t="s">
+        <v>703</v>
+      </c>
+      <c r="D699">
+        <v>3.5528578317261044</v>
+      </c>
+      <c r="E699">
+        <v>-1.6676761004639218E-3</v>
+      </c>
+      <c r="F699" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G699" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="700" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A700" t="s">
+        <v>532</v>
+      </c>
+      <c r="B700" t="s">
+        <v>667</v>
+      </c>
+      <c r="C700" t="s">
+        <v>703</v>
+      </c>
+      <c r="D700">
+        <v>3.6743909390447942</v>
+      </c>
+      <c r="E700">
+        <v>-6.1894537077641409</v>
+      </c>
+      <c r="F700" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G700" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="701" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A701" t="s">
+        <v>532</v>
+      </c>
+      <c r="B701" t="s">
+        <v>668</v>
+      </c>
+      <c r="C701" t="s">
+        <v>703</v>
+      </c>
+      <c r="D701">
+        <v>4.3167626095534528</v>
+      </c>
+      <c r="E701">
+        <v>-9.0878417002477789</v>
+      </c>
+      <c r="F701" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G701" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="702" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A702" t="s">
+        <v>532</v>
+      </c>
+      <c r="B702" t="s">
+        <v>669</v>
+      </c>
+      <c r="C702" t="s">
+        <v>703</v>
+      </c>
+      <c r="D702">
+        <v>4.6098197775262246</v>
+      </c>
+      <c r="E702">
+        <v>-11.295468617891032</v>
+      </c>
+      <c r="F702" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G702" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="703" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A703" t="s">
+        <v>532</v>
+      </c>
+      <c r="B703" t="s">
+        <v>670</v>
+      </c>
+      <c r="C703" t="s">
+        <v>703</v>
+      </c>
+      <c r="D703">
+        <v>4.5950407072821218</v>
+      </c>
+      <c r="E703">
+        <v>-12.997802679895411</v>
+      </c>
+      <c r="F703" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G703" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="704" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A704" t="s">
+        <v>532</v>
+      </c>
+      <c r="B704" t="s">
+        <v>671</v>
+      </c>
+      <c r="C704" t="s">
+        <v>703</v>
+      </c>
+      <c r="D704">
+        <v>4.7577749521061667</v>
+      </c>
+      <c r="E704">
+        <v>-14.239774697671496</v>
+      </c>
+      <c r="F704" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G704" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="705" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A705" t="s">
+        <v>532</v>
+      </c>
+      <c r="B705" t="s">
+        <v>672</v>
+      </c>
+      <c r="C705" t="s">
+        <v>703</v>
+      </c>
+      <c r="D705">
+        <v>4.385420455976206</v>
+      </c>
+      <c r="E705">
+        <v>-14.937464534369299</v>
+      </c>
+      <c r="F705" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G705" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="706" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A706" t="s">
+        <v>532</v>
+      </c>
+      <c r="B706" t="s">
+        <v>673</v>
+      </c>
+      <c r="C706" t="s">
+        <v>703</v>
+      </c>
+      <c r="D706">
+        <v>3.709807066759109</v>
+      </c>
+      <c r="E706">
+        <v>-15.735197237963966</v>
+      </c>
+      <c r="F706" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G706" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="707" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A707" t="s">
+        <v>532</v>
+      </c>
+      <c r="B707" t="s">
+        <v>674</v>
+      </c>
+      <c r="C707" t="s">
+        <v>703</v>
+      </c>
+      <c r="D707">
+        <v>10.574963562589717</v>
+      </c>
+      <c r="E707">
+        <v>104.47660177378756</v>
+      </c>
+      <c r="F707" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G707" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A708" t="s">
+        <v>532</v>
+      </c>
+      <c r="B708" t="s">
+        <v>675</v>
+      </c>
+      <c r="C708" t="s">
+        <v>703</v>
+      </c>
+      <c r="D708">
+        <v>6.8830951747915865</v>
+      </c>
+      <c r="E708">
+        <v>-14.377533214889297</v>
+      </c>
+      <c r="F708" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G708" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="709" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A709" t="s">
+        <v>532</v>
+      </c>
+      <c r="B709" t="s">
+        <v>676</v>
+      </c>
+      <c r="C709" t="s">
+        <v>703</v>
+      </c>
+      <c r="D709">
+        <v>6.1422227579420765</v>
+      </c>
+      <c r="E709">
+        <v>30.42686157489754</v>
+      </c>
+      <c r="F709" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G709" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="710" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A710" t="s">
+        <v>532</v>
+      </c>
+      <c r="B710" t="s">
+        <v>677</v>
+      </c>
+      <c r="C710" t="s">
+        <v>703</v>
+      </c>
+      <c r="D710">
+        <v>4.3057366532967603</v>
+      </c>
+      <c r="E710">
+        <v>17.361909488896117</v>
+      </c>
+      <c r="F710" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G710" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="711" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A711" t="s">
+        <v>532</v>
+      </c>
+      <c r="B711" t="s">
+        <v>678</v>
+      </c>
+      <c r="C711" t="s">
+        <v>703</v>
+      </c>
+      <c r="D711">
+        <v>4.5906448568250973</v>
+      </c>
+      <c r="E711">
+        <v>-2.6923980146794761</v>
+      </c>
+      <c r="F711" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G711" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="712" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A712" t="s">
+        <v>532</v>
+      </c>
+      <c r="B712" t="s">
+        <v>679</v>
+      </c>
+      <c r="C712" t="s">
+        <v>703</v>
+      </c>
+      <c r="D712">
+        <v>6.2418070667266088</v>
+      </c>
+      <c r="E712">
+        <v>-8.0103235210955752</v>
+      </c>
+      <c r="F712" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G712" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="713" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A713" t="s">
+        <v>532</v>
+      </c>
+      <c r="B713" t="s">
+        <v>680</v>
+      </c>
+      <c r="C713" t="s">
+        <v>703</v>
+      </c>
+      <c r="D713">
+        <v>7.3695059991500331</v>
+      </c>
+      <c r="E713">
+        <v>-11.826827710515886</v>
+      </c>
+      <c r="F713" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G713" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="714" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A714" t="s">
+        <v>532</v>
+      </c>
+      <c r="B714" t="s">
+        <v>681</v>
+      </c>
+      <c r="C714" t="s">
+        <v>703</v>
+      </c>
+      <c r="D714">
+        <v>7.8924956956445964</v>
+      </c>
+      <c r="E714">
+        <v>-12.648159078776867</v>
+      </c>
+      <c r="F714" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G714" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A715" t="s">
+        <v>532</v>
+      </c>
+      <c r="B715" t="s">
+        <v>682</v>
+      </c>
+      <c r="C715" t="s">
+        <v>703</v>
+      </c>
+      <c r="D715">
+        <v>9.553158411159119</v>
+      </c>
+      <c r="E715">
+        <v>-14.069339724474819</v>
+      </c>
+      <c r="F715" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G715" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A716" t="s">
+        <v>532</v>
+      </c>
+      <c r="B716" t="s">
+        <v>683</v>
+      </c>
+      <c r="C716" t="s">
+        <v>703</v>
+      </c>
+      <c r="D716">
+        <v>9.3980221636353427</v>
+      </c>
+      <c r="E716">
+        <v>-13.604657022455683</v>
+      </c>
+      <c r="F716" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G716" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A717" t="s">
+        <v>532</v>
+      </c>
+      <c r="B717" t="s">
+        <v>684</v>
+      </c>
+      <c r="C717" t="s">
+        <v>703</v>
+      </c>
+      <c r="D717">
+        <v>0.77106064941587205</v>
+      </c>
+      <c r="E717">
+        <v>424.8982823587707</v>
+      </c>
+      <c r="F717" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G717" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A718" t="s">
+        <v>532</v>
+      </c>
+      <c r="B718" t="s">
+        <v>685</v>
+      </c>
+      <c r="C718" t="s">
+        <v>703</v>
+      </c>
+      <c r="D718">
+        <v>0.1062495712177698</v>
+      </c>
+      <c r="E718">
+        <v>-2.8008809580421286</v>
+      </c>
+      <c r="F718" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G718" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="719" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A719" t="s">
+        <v>532</v>
+      </c>
+      <c r="B719" t="s">
+        <v>686</v>
+      </c>
+      <c r="C719" t="s">
+        <v>703</v>
+      </c>
+      <c r="D719">
+        <v>0.21289625123999523</v>
+      </c>
+      <c r="E719">
+        <v>24.631785829340391</v>
+      </c>
+      <c r="F719" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G719" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="720" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A720" t="s">
+        <v>532</v>
+      </c>
+      <c r="B720" t="s">
+        <v>687</v>
+      </c>
+      <c r="C720" t="s">
+        <v>703</v>
+      </c>
+      <c r="D720">
+        <v>0.18573415986168115</v>
+      </c>
+      <c r="E720">
+        <v>4.1617715561843589</v>
+      </c>
+      <c r="F720" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G720" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="721" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A721" t="s">
+        <v>532</v>
+      </c>
+      <c r="B721" t="s">
+        <v>688</v>
+      </c>
+      <c r="C721" t="s">
+        <v>703</v>
+      </c>
+      <c r="D721">
+        <v>0.17722576416722091</v>
+      </c>
+      <c r="E721">
+        <v>-0.40359366323464485</v>
+      </c>
+      <c r="F721" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G721" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="722" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A722" t="s">
+        <v>532</v>
+      </c>
+      <c r="B722" t="s">
+        <v>689</v>
+      </c>
+      <c r="C722" t="s">
+        <v>703</v>
+      </c>
+      <c r="D722">
+        <v>0.15545132842257833</v>
+      </c>
+      <c r="E722">
+        <v>-0.34152873685061635</v>
+      </c>
+      <c r="F722" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G722" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="723" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A723" t="s">
+        <v>532</v>
+      </c>
+      <c r="B723" t="s">
+        <v>690</v>
+      </c>
+      <c r="C723" t="s">
+        <v>703</v>
+      </c>
+      <c r="D723">
+        <v>0.14649041800740731</v>
+      </c>
+      <c r="E723">
+        <v>-3.6178127029762912</v>
+      </c>
+      <c r="F723" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G723" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="724" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A724" t="s">
+        <v>532</v>
+      </c>
+      <c r="B724" t="s">
+        <v>691</v>
+      </c>
+      <c r="C724" t="s">
+        <v>703</v>
+      </c>
+      <c r="D724">
+        <v>0.12363028597506719</v>
+      </c>
+      <c r="E724">
+        <v>-4.0524552780430412</v>
+      </c>
+      <c r="F724" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G724" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="725" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A725" t="s">
+        <v>532</v>
+      </c>
+      <c r="B725" t="s">
+        <v>692</v>
+      </c>
+      <c r="C725" t="s">
+        <v>703</v>
+      </c>
+      <c r="D725">
+        <v>0.11841019444007879</v>
+      </c>
+      <c r="E725">
+        <v>-1.7637262187159557</v>
+      </c>
+      <c r="F725" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G725" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="726" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A726" t="s">
+        <v>532</v>
+      </c>
+      <c r="B726" t="s">
+        <v>693</v>
+      </c>
+      <c r="C726" t="s">
+        <v>703</v>
+      </c>
+      <c r="D726">
+        <v>0.13360864917659027</v>
+      </c>
+      <c r="E726">
+        <v>-4.3782762166051086</v>
+      </c>
+      <c r="F726" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G726" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="727" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A727" t="s">
+        <v>532</v>
+      </c>
+      <c r="B727" t="s">
+        <v>694</v>
+      </c>
+      <c r="C727" t="s">
+        <v>703</v>
+      </c>
+      <c r="D727">
+        <v>7.4268779832919236</v>
+      </c>
+      <c r="E727">
+        <v>-16.678696384545908</v>
+      </c>
+      <c r="F727" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G727" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="728" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A728" t="s">
+        <v>532</v>
+      </c>
+      <c r="B728" t="s">
+        <v>695</v>
+      </c>
+      <c r="C728" t="s">
+        <v>703</v>
+      </c>
+      <c r="D728">
+        <v>4.3239117640847926</v>
+      </c>
+      <c r="E728">
+        <v>-16.063985603946982</v>
+      </c>
+      <c r="F728" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G728" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="729" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A729" t="s">
+        <v>532</v>
+      </c>
+      <c r="B729" t="s">
+        <v>696</v>
+      </c>
+      <c r="C729" t="s">
+        <v>703</v>
+      </c>
+      <c r="D729">
+        <v>4.3271664579994029</v>
+      </c>
+      <c r="E729">
+        <v>-16.434120047256176</v>
+      </c>
+      <c r="F729" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G729" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="730" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A730" t="s">
+        <v>532</v>
+      </c>
+      <c r="B730" t="s">
+        <v>697</v>
+      </c>
+      <c r="C730" t="s">
+        <v>703</v>
+      </c>
+      <c r="D730">
+        <v>3.3013172353828071</v>
+      </c>
+      <c r="E730">
+        <v>-16.536940892855931</v>
+      </c>
+      <c r="F730" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G730" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="731" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A731" t="s">
+        <v>532</v>
+      </c>
+      <c r="B731" t="s">
+        <v>698</v>
+      </c>
+      <c r="C731" t="s">
+        <v>703</v>
+      </c>
+      <c r="D731">
+        <v>3.9147414611774769</v>
+      </c>
+      <c r="E731">
+        <v>-17.296397146713417</v>
+      </c>
+      <c r="F731" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G731" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="732" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A732" t="s">
+        <v>532</v>
+      </c>
+      <c r="B732" t="s">
+        <v>699</v>
+      </c>
+      <c r="C732" t="s">
+        <v>703</v>
+      </c>
+      <c r="D732">
+        <v>4.3294347564753402</v>
+      </c>
+      <c r="E732">
+        <v>-16.301952175667758</v>
+      </c>
+      <c r="F732" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G732" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="733" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A733" t="s">
+        <v>532</v>
+      </c>
+      <c r="B733" t="s">
+        <v>700</v>
+      </c>
+      <c r="C733" t="s">
+        <v>703</v>
+      </c>
+      <c r="D733">
+        <v>3.9172438839316004</v>
+      </c>
+      <c r="E733">
+        <v>-16.054100276356419</v>
+      </c>
+      <c r="F733" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G733" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="734" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A734" t="s">
+        <v>532</v>
+      </c>
+      <c r="B734" t="s">
+        <v>701</v>
+      </c>
+      <c r="C734" t="s">
+        <v>703</v>
+      </c>
+      <c r="D734">
+        <v>4.6260376939314831</v>
+      </c>
+      <c r="E734">
+        <v>-16.313890299161827</v>
+      </c>
+      <c r="F734" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G734" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="735" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A735" t="s">
+        <v>532</v>
+      </c>
+      <c r="B735" t="s">
+        <v>702</v>
+      </c>
+      <c r="C735" t="s">
+        <v>703</v>
+      </c>
+      <c r="D735">
+        <v>3.1791240109164653</v>
+      </c>
+      <c r="E735">
+        <v>-26.018771175508743</v>
+      </c>
+      <c r="F735" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G735" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
